--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/01,26/12,01,26 Ост СЫР филиалы/Мелитополь/дв 12,01,26 млрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/01,26/12,01,26 Ост СЫР филиалы/Мелитополь/дв 12,01,26 млрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\РАБОЧИЙ СТОЛ\12,01,26 Ост СЫР филиалы\Мелитополь\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\01,26\12,01,26 Ост СЫР филиалы\Мелитополь\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BD6881-46D3-4956-A686-784FB0E0C157}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E280B-C4BD-4C22-AC25-6E68D226B59D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,6 +388,18 @@
     <xf numFmtId="165" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -408,18 +420,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -810,50 +810,50 @@
         <v>4</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
     </row>
     <row r="9" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="21"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="4" t="s">
         <v>11</v>
       </c>
@@ -877,19 +877,19 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="16">
         <v>12</v>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="6">
         <v>204</v>
       </c>
@@ -913,19 +913,19 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="16">
         <v>246</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="6">
         <v>204</v>
       </c>
@@ -949,12 +949,12 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="5" t="s">
         <v>19</v>
       </c>
@@ -977,19 +977,19 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="16">
         <v>66</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="6">
         <v>804</v>
       </c>
@@ -1013,12 +1013,12 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="5" t="s">
         <v>19</v>
       </c>
@@ -1041,12 +1041,12 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
       <c r="E15" s="5" t="s">
         <v>19</v>
       </c>
@@ -1069,12 +1069,12 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
       <c r="E16" s="5" t="s">
         <v>19</v>
       </c>
@@ -1097,19 +1097,19 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
       <c r="E17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="16">
         <v>275</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="6">
         <v>32</v>
       </c>
@@ -1133,19 +1133,19 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
       <c r="E18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="16">
         <v>138</v>
       </c>
-      <c r="G18" s="23"/>
+      <c r="G18" s="16"/>
       <c r="H18" s="6">
         <v>128</v>
       </c>
@@ -1169,19 +1169,19 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="16">
         <v>300</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="10">
         <v>1500</v>
       </c>
@@ -1205,19 +1205,19 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
       <c r="E20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="18">
         <v>2009</v>
       </c>
-      <c r="G20" s="24"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="9"/>
       <c r="I20" s="6">
         <v>930</v>
@@ -1237,19 +1237,19 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="16">
         <v>44</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="16"/>
       <c r="H21" s="6">
         <v>28</v>
       </c>
@@ -1273,19 +1273,19 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
       <c r="E22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="16">
         <v>144</v>
       </c>
-      <c r="G22" s="23"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="9"/>
       <c r="I22" s="6">
         <v>19</v>
@@ -1305,19 +1305,19 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
       <c r="E23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="16">
         <v>-25</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="16"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="6">
@@ -1333,19 +1333,19 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
       <c r="E24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="16">
         <v>507</v>
       </c>
-      <c r="G24" s="23"/>
+      <c r="G24" s="16"/>
       <c r="H24" s="6">
         <v>102</v>
       </c>
@@ -1369,19 +1369,19 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
       <c r="E25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="16">
         <v>51</v>
       </c>
-      <c r="G25" s="23"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="6">
         <v>2</v>
       </c>
@@ -1405,19 +1405,19 @@
       </c>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
       <c r="E26" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="16">
         <v>900</v>
       </c>
-      <c r="G26" s="23"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="6">
         <v>202</v>
       </c>
@@ -1441,19 +1441,19 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="16">
         <v>624</v>
       </c>
-      <c r="G27" s="23"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="6">
         <v>292</v>
       </c>
@@ -1477,19 +1477,19 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="16">
         <v>140</v>
       </c>
-      <c r="G28" s="23"/>
+      <c r="G28" s="16"/>
       <c r="H28" s="9"/>
       <c r="I28" s="6">
         <v>139</v>
@@ -1509,19 +1509,19 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
       <c r="E29" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="16">
         <v>-20</v>
       </c>
-      <c r="G29" s="23"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="6">
         <v>30</v>
       </c>
@@ -1541,19 +1541,19 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
       <c r="E30" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="18">
         <v>1071</v>
       </c>
-      <c r="G30" s="24"/>
+      <c r="G30" s="18"/>
       <c r="H30" s="6">
         <v>2</v>
       </c>
@@ -1577,19 +1577,19 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
       <c r="E31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="16">
         <v>667</v>
       </c>
-      <c r="G31" s="23"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="9"/>
       <c r="I31" s="6">
         <v>348</v>
@@ -1609,19 +1609,19 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
       <c r="E32" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="16">
         <v>218</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="16"/>
       <c r="H32" s="6">
         <v>304</v>
       </c>
@@ -1645,19 +1645,19 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
       <c r="E33" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="16">
         <v>87.06</v>
       </c>
-      <c r="G33" s="23"/>
+      <c r="G33" s="16"/>
       <c r="H33" s="6">
         <v>92.543999999999997</v>
       </c>
@@ -1681,19 +1681,19 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
       <c r="E34" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="16">
         <v>222.64400000000001</v>
       </c>
-      <c r="G34" s="23"/>
+      <c r="G34" s="16"/>
       <c r="H34" s="6">
         <v>187.74799999999999</v>
       </c>
@@ -1717,19 +1717,19 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
       <c r="E35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="16">
         <v>262.23</v>
       </c>
-      <c r="G35" s="23"/>
+      <c r="G35" s="16"/>
       <c r="H35" s="9"/>
       <c r="I35" s="6">
         <v>213.31100000000001</v>
@@ -1749,19 +1749,19 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
       <c r="E36" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="16">
         <v>72</v>
       </c>
-      <c r="G36" s="23"/>
+      <c r="G36" s="16"/>
       <c r="H36" s="6">
         <v>168</v>
       </c>
@@ -1785,12 +1785,12 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
       <c r="E37" s="5" t="s">
         <v>19</v>
       </c>
@@ -1813,19 +1813,19 @@
       </c>
     </row>
     <row r="38" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
       <c r="E38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="16">
         <v>-20</v>
       </c>
-      <c r="G38" s="23"/>
+      <c r="G38" s="16"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="6">
@@ -1841,19 +1841,19 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
       <c r="E39" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="16">
         <v>90</v>
       </c>
-      <c r="G39" s="23"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="9"/>
       <c r="I39" s="6">
         <v>90</v>
@@ -1869,19 +1869,19 @@
       <c r="N39" s="9"/>
     </row>
     <row r="40" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
       <c r="E40" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="16">
         <v>347</v>
       </c>
-      <c r="G40" s="23"/>
+      <c r="G40" s="16"/>
       <c r="H40" s="9"/>
       <c r="I40" s="6">
         <v>88</v>
@@ -1901,19 +1901,19 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
       <c r="E41" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="16">
         <v>349</v>
       </c>
-      <c r="G41" s="23"/>
+      <c r="G41" s="16"/>
       <c r="H41" s="6">
         <v>300</v>
       </c>
@@ -1937,19 +1937,19 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
       <c r="E42" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="16">
         <v>146.554</v>
       </c>
-      <c r="G42" s="23"/>
+      <c r="G42" s="16"/>
       <c r="H42" s="6">
         <v>474.52800000000002</v>
       </c>
@@ -1973,19 +1973,19 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
       <c r="E43" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="16">
         <v>408</v>
       </c>
-      <c r="G43" s="23"/>
+      <c r="G43" s="16"/>
       <c r="H43" s="6">
         <v>406</v>
       </c>
@@ -2009,12 +2009,12 @@
       </c>
     </row>
     <row r="44" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
       <c r="E44" s="5" t="s">
         <v>19</v>
       </c>
@@ -2037,19 +2037,19 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
       <c r="E45" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="16">
         <v>743.45799999999997</v>
       </c>
-      <c r="G45" s="23"/>
+      <c r="G45" s="16"/>
       <c r="H45" s="6">
         <v>17.774000000000001</v>
       </c>
@@ -2073,12 +2073,12 @@
       </c>
     </row>
     <row r="46" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
       <c r="E46" s="5" t="s">
         <v>33</v>
       </c>
@@ -2101,13 +2101,13 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="11"/>
       <c r="G47" s="12"/>
       <c r="H47" s="13"/>
@@ -2128,80 +2128,80 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:E47"/>
   </mergeCells>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
